--- a/exports/UserListTemplate.xlsx
+++ b/exports/UserListTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AD-ICT\Agricensus2026\acsl2026\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12C0080-5C25-463E-954E-C073A27EEA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8973F-AB50-469C-B191-1313390AC64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC5B067A-78CF-4E38-9D6B-CEC5B0700BC6}"/>
   </bookViews>
